--- a/1_PREPARE_TRAIN_UNET_DATA/TriuksmaiAnotacijosDuomenyse2023/template_anotavimo_logas.xlsx
+++ b/1_PREPARE_TRAIN_UNET_DATA/TriuksmaiAnotacijosDuomenyse2023/template_anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\1_PREPARE_TRAIN_UNET_DATA\TriuksmaiAnotacijosDuomenyse2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D8AFA7-3C95-449A-975F-7A7F4002AA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA02866-156A-4081-AC1B-38B9357DC2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>file_name</t>
-  </si>
-  <si>
     <t>rec_id</t>
   </si>
   <si>
@@ -82,6 +79,9 @@
   </si>
   <si>
     <t>1742362.474</t>
+  </si>
+  <si>
+    <t>filename</t>
   </si>
 </sst>
 </file>
@@ -89,8 +89,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -159,14 +159,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -481,218 +480,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="4"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="2"/>
+      <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="4"/>
+      <c r="H3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="2"/>
+      <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="4"/>
+      <c r="H4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="2"/>
+      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="4"/>
+      <c r="H5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="2"/>
+      <c r="X5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
